--- a/input/linkSanPham.xlsx
+++ b/input/linkSanPham.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
     <t>Name Acc</t>
   </si>
@@ -41,10 +41,37 @@
     <t>VPN-TOOL-THIET</t>
   </si>
   <si>
-    <t>DUY0603</t>
-  </si>
-  <si>
-    <t>https://www.sheshow.com/rodeo-bikini-set-for-women/</t>
+    <t>https://vm.tiktok.com/ZP9d9dhRS9cvX-UINfs/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9dym1pnFj-YoZJ3/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9dASJmver-5AaLo/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9dDGPMUra-vUw1P/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9duwNw7Bp-XUAeC/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9d5PQMpSc-cNRT6/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9duwNw7kA-7fssz/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9dCGwhRo3-vyQ9n/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9dQ74e3Qa-vjVwS/</t>
+  </si>
+  <si>
+    <t>https://vm.tiktok.com/ZP9d9dCWGARYQ-KbhL8/</t>
+  </si>
+  <si>
+    <t>HAT0903</t>
   </si>
 </sst>
 </file>
@@ -60,15 +87,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FFBCBEC4"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF01162B"/>
       <name val="GoogleSans-Regular"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -79,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -87,20 +116,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -387,7 +451,7 @@
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,109 +465,193 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2"/>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
+      <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
+      <c r="A15" s="1"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
+      <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="2"/>
+      <c r="A17" s="1"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="2"/>
+      <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="2"/>
+      <c r="A19" s="1"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="2"/>
+      <c r="A20" s="1"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="2"/>
+      <c r="A21" s="1"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="2"/>
+      <c r="A22" s="1"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="2"/>
+      <c r="A23" s="1"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="2"/>
+      <c r="A24" s="1"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="2"/>
+      <c r="A25" s="1"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="2"/>
+      <c r="A26" s="1"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="2"/>
+      <c r="A27" s="1"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="2"/>
+      <c r="A28" s="1"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="2"/>
+      <c r="A29" s="1"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="2"/>
+      <c r="A30" s="1"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="2"/>
+      <c r="A31" s="1"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="2"/>
+      <c r="A32" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="B7" r:id="rId6"/>
+    <hyperlink ref="B8" r:id="rId7"/>
+    <hyperlink ref="B9" r:id="rId8"/>
+    <hyperlink ref="B10" r:id="rId9"/>
+    <hyperlink ref="B11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
--- a/input/linkSanPham.xlsx
+++ b/input/linkSanPham.xlsx
@@ -41,6 +41,9 @@
     <t>VPN-TOOL-THIET</t>
   </si>
   <si>
+    <t>etsyLHv21003</t>
+  </si>
+  <si>
     <t>https://vm.tiktok.com/ZP9d9dhRS9cvX-UINfs/</t>
   </si>
   <si>
@@ -69,9 +72,6 @@
   </si>
   <si>
     <t>https://vm.tiktok.com/ZP9d9dCWGARYQ-KbhL8/</t>
-  </si>
-  <si>
-    <t>HAT0903</t>
   </si>
 </sst>
 </file>
@@ -443,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -470,10 +470,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1">
@@ -481,10 +481,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1">
@@ -492,10 +492,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1">
@@ -503,10 +503,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1">
@@ -514,10 +514,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1">
@@ -525,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1">
@@ -536,10 +536,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1">
@@ -547,10 +547,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1">
@@ -558,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" thickBot="1">
@@ -569,10 +569,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -637,6 +637,45 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/input/linkSanPham.xlsx
+++ b/input/linkSanPham.xlsx
@@ -41,9 +41,6 @@
     <t>VPN-TOOL-THIET</t>
   </si>
   <si>
-    <t>etsyLHv21003</t>
-  </si>
-  <si>
     <t>https://vm.tiktok.com/ZP9d9dhRS9cvX-UINfs/</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>https://vm.tiktok.com/ZP9d9dCWGARYQ-KbhL8/</t>
+  </si>
+  <si>
+    <t>tesst1</t>
   </si>
 </sst>
 </file>
@@ -470,10 +470,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1">
@@ -481,10 +481,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1">
@@ -492,10 +492,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1">
@@ -503,10 +503,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1">
@@ -514,10 +514,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1">
@@ -525,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1">
@@ -536,10 +536,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1">
@@ -547,10 +547,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1">
@@ -558,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" thickBot="1">
@@ -569,10 +569,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">

--- a/input/linkSanPham.xlsx
+++ b/input/linkSanPham.xlsx
@@ -41,44 +41,44 @@
     <t>VPN-TOOL-THIET</t>
   </si>
   <si>
-    <t>https://vm.tiktok.com/ZP9d9dhRS9cvX-UINfs/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9dym1pnFj-YoZJ3/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9dASJmver-5AaLo/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9dDGPMUra-vUw1P/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9duwNw7Bp-XUAeC/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9d5PQMpSc-cNRT6/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9duwNw7kA-7fssz/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9dCGwhRo3-vyQ9n/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9dQ74e3Qa-vjVwS/</t>
-  </si>
-  <si>
-    <t>https://vm.tiktok.com/ZP9d9dCWGARYQ-KbhL8/</t>
-  </si>
-  <si>
-    <t>tesst1</t>
+    <t>HAT1203</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4439732209/mustache-lover-hat-embroidered-baseball?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-1-10&amp;pro=1&amp;plkey=Eu1fw9BKb1wRUlNcKxkhI1uBzV82%3ALTcf4bc07e616b33d72cd67db8bd8150279916d282</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/793747349/n-vaporwave-retro-gaming-embroidered-hat?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-1-11&amp;frs=1&amp;sts=1&amp;content_source=5e874c39-62e5-434c-9aa2-34065d629871%253ALTc67878e3ab0a40906464dff12f99a238151d7a0e&amp;organic_search_click=1&amp;logging_key=5e874c39-62e5-434c-9aa2-34065d629871%3ALTc67878e3ab0a40906464dff12f99a238151d7a0e</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/1897102709/premium-black-cat-embroidered-dad-hat?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-1-10&amp;pro=1&amp;frs=1&amp;bes=1&amp;content_source=5e874c39-62e5-434c-9aa2-34065d629871%253ALT99fd912a174078e29660501987f7a28e068e9fd3&amp;organic_search_click=1&amp;logging_key=5e874c39-62e5-434c-9aa2-34065d629871%3ALT99fd912a174078e29660501987f7a28e068e9fd3</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4372928507/embroidered-raven-crow-coffee-hat-hello?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-3-23&amp;pro=1&amp;content_source=3c19f3eb-1ad3-48bd-a3b3-eca0809ecaab%253ALTc05429c354c38e994dda2b467c7cd0e34b597555&amp;organic_search_click=1&amp;logging_key=3c19f3eb-1ad3-48bd-a3b3-eca0809ecaab%3ALTc05429c354c38e994dda2b467c7cd0e34b597555</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4314103606/girldad-3d-puff-embroidered-classic?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-3-5&amp;frs=1&amp;sts=1&amp;plkey=EurH50gIg_FPM04eof8_Z4C5Wy1b%3ALT236ab27760ee7fa8036f83061f8d66fd417a9985</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4408049296/3d-puff-mama-gang-trendy-hat?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-3-11&amp;sca=1&amp;plkey=EurH50gIg_FPM04eof8_Z4C5Wy1b%3ALT05cc04546cbf73ded66056c0a723aa5ba286b30a</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/1858259624/put-it-on-my-husbands-tab-hat-5-panel?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-2-10&amp;frs=1&amp;pop=1&amp;sts=1&amp;plkey=EuSq83tU8FSMzLvcQvj3IjWWP3d9%3ALTc40e2372fa44d00f3b36ca2195fa84292040405a</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4392275041/embroidered-washed-baseball-cap-big-fan?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-2-4&amp;pro=1&amp;bes=1&amp;content_source=e61d3297-8843-4683-8979-e36e459d650e%253ALT1c6230f7af30975455f507c195c6bb7f66af9a00&amp;organic_search_click=1&amp;logging_key=e61d3297-8843-4683-8979-e36e459d650e%3ALT1c6230f7af30975455f507c195c6bb7f66af9a00</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4457439053/spritz-hatspritz-lover-hatspritz?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-1-4&amp;pro=1&amp;pop=1&amp;plkey=Eu1fw9BKb1wRUlNcKxkhI1uBzV82%3ALT1d40a25ff780085f9eccd16db644557987bb0f05</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4464660870/usa-45-47-america-hat-america-patriotic?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-1-5&amp;pro=1&amp;plkey=Eu1fw9BKb1wRUlNcKxkhI1uBzV82%3ALTcc701167939971f09d7a51ea486a34686eb8293d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +90,12 @@
       <sz val="10"/>
       <color rgb="FF01162B"/>
       <name val="GoogleSans-Regular"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
     <font>
       <u/>
@@ -108,27 +114,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -149,17 +140,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -443,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -465,232 +456,466 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1">
+    <row r="2" spans="1:4" ht="120.75" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="1:4" ht="180.75" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="1"/>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="1"/>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="1"/>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="1"/>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1"/>
+      <c r="B52" s="2"/>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1"/>
+      <c r="B53" s="2"/>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1"/>
+      <c r="B54" s="2"/>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1"/>
+      <c r="B55" s="2"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1"/>
+      <c r="B56" s="2"/>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1"/>
+      <c r="B61" s="2"/>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1"/>
+      <c r="B62" s="2"/>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2"/>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2"/>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1"/>
+      <c r="B65" s="2"/>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1"/>
+      <c r="B66" s="2"/>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="1"/>
+      <c r="B67" s="2"/>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="1"/>
+      <c r="B69" s="2"/>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="1"/>
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="2"/>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="1"/>
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1"/>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1"/>
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1"/>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1"/>
+      <c r="B80" s="2"/>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1"/>
+      <c r="B81" s="2"/>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1"/>
+      <c r="B82" s="2"/>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1"/>
+      <c r="B83" s="2"/>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1"/>
+      <c r="B84" s="2"/>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1"/>
+      <c r="B85" s="2"/>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1"/>
+      <c r="B86" s="2"/>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="1"/>
+      <c r="B87" s="2"/>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="1"/>
+      <c r="B88" s="2"/>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="1"/>
+      <c r="B89" s="2"/>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="1"/>
+      <c r="B90" s="2"/>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="1"/>
+      <c r="B91" s="2"/>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="1"/>
+      <c r="B92" s="2"/>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="1"/>
+      <c r="B93" s="2"/>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="1"/>
+      <c r="B94" s="2"/>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="1"/>
+      <c r="B95" s="2"/>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="1"/>
+      <c r="B96" s="2"/>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="1"/>
+      <c r="B97" s="2"/>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="1"/>
+      <c r="B98" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B8" r:id="rId7"/>
-    <hyperlink ref="B9" r:id="rId8"/>
-    <hyperlink ref="B10" r:id="rId9"/>
-    <hyperlink ref="B11" r:id="rId10"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/input/linkSanPham.xlsx
+++ b/input/linkSanPham.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="21">
   <si>
     <t>Name Acc</t>
   </si>
@@ -41,37 +41,52 @@
     <t>VPN-TOOL-THIET</t>
   </si>
   <si>
-    <t>HAT1203</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4439732209/mustache-lover-hat-embroidered-baseball?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-1-10&amp;pro=1&amp;plkey=Eu1fw9BKb1wRUlNcKxkhI1uBzV82%3ALTcf4bc07e616b33d72cd67db8bd8150279916d282</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/793747349/n-vaporwave-retro-gaming-embroidered-hat?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-1-11&amp;frs=1&amp;sts=1&amp;content_source=5e874c39-62e5-434c-9aa2-34065d629871%253ALTc67878e3ab0a40906464dff12f99a238151d7a0e&amp;organic_search_click=1&amp;logging_key=5e874c39-62e5-434c-9aa2-34065d629871%3ALTc67878e3ab0a40906464dff12f99a238151d7a0e</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/1897102709/premium-black-cat-embroidered-dad-hat?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-1-10&amp;pro=1&amp;frs=1&amp;bes=1&amp;content_source=5e874c39-62e5-434c-9aa2-34065d629871%253ALT99fd912a174078e29660501987f7a28e068e9fd3&amp;organic_search_click=1&amp;logging_key=5e874c39-62e5-434c-9aa2-34065d629871%3ALT99fd912a174078e29660501987f7a28e068e9fd3</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4372928507/embroidered-raven-crow-coffee-hat-hello?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-3-23&amp;pro=1&amp;content_source=3c19f3eb-1ad3-48bd-a3b3-eca0809ecaab%253ALTc05429c354c38e994dda2b467c7cd0e34b597555&amp;organic_search_click=1&amp;logging_key=3c19f3eb-1ad3-48bd-a3b3-eca0809ecaab%3ALTc05429c354c38e994dda2b467c7cd0e34b597555</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4314103606/girldad-3d-puff-embroidered-classic?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-3-5&amp;frs=1&amp;sts=1&amp;plkey=EurH50gIg_FPM04eof8_Z4C5Wy1b%3ALT236ab27760ee7fa8036f83061f8d66fd417a9985</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4408049296/3d-puff-mama-gang-trendy-hat?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-3-11&amp;sca=1&amp;plkey=EurH50gIg_FPM04eof8_Z4C5Wy1b%3ALT05cc04546cbf73ded66056c0a723aa5ba286b30a</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/1858259624/put-it-on-my-husbands-tab-hat-5-panel?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-2-10&amp;frs=1&amp;pop=1&amp;sts=1&amp;plkey=EuSq83tU8FSMzLvcQvj3IjWWP3d9%3ALTc40e2372fa44d00f3b36ca2195fa84292040405a</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4392275041/embroidered-washed-baseball-cap-big-fan?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sr_gallery-2-4&amp;pro=1&amp;bes=1&amp;content_source=e61d3297-8843-4683-8979-e36e459d650e%253ALT1c6230f7af30975455f507c195c6bb7f66af9a00&amp;organic_search_click=1&amp;logging_key=e61d3297-8843-4683-8979-e36e459d650e%3ALT1c6230f7af30975455f507c195c6bb7f66af9a00</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4457439053/spritz-hatspritz-lover-hatspritz?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-1-4&amp;pro=1&amp;pop=1&amp;plkey=Eu1fw9BKb1wRUlNcKxkhI1uBzV82%3ALT1d40a25ff780085f9eccd16db644557987bb0f05</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4464660870/usa-45-47-america-hat-america-patriotic?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=hat&amp;ref=sc_gallery-1-5&amp;pro=1&amp;plkey=Eu1fw9BKb1wRUlNcKxkhI1uBzV82%3ALTcc701167939971f09d7a51ea486a34686eb8293d</t>
+    <t>https://www.etsy.com/listing/4468133183/harry-styles-tour-2026-t-shirt-2-sided?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-1&amp;pro=1&amp;pop=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT49d7bb0973ada13d81acc0b91a5c26240b4c9070&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT49d7bb0973ada13d81acc0b91a5c26240b4c9070</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4467439062/cardi-b-little-miss-drama-png-bundle?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=digital+hot&amp;ref=sr_gallery-1-30&amp;pro=1&amp;pop=1&amp;dd=1&amp;content_source=2abb1d39-7b0f-4bc1-bb8d-d43650e25d91%253ALT15a94dab7eede1dc58bd3a80961a0e21ce6ad8dc&amp;organic_search_click=1&amp;logging_key=2abb1d39-7b0f-4bc1-bb8d-d43650e25d91%3ALT15a94dab7eede1dc58bd3a80961a0e21ce6ad8dc</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4465475509/b2k-bow-wow-boys4life-tour-png-file-b2k?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sc_gallery-1-1&amp;bes=1&amp;dd=1&amp;plkey=EuT5L3uuuid6SYAbqvplfKbowzdc%3ALTd3104fd06d8f578090cfd50cf43c7823b1f31846</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4465319382/conan-gray-wishbone-world-tour-2026-tour?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-3&amp;pop=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALTc7203525a63f93388f4ea79e89e80b036f5441bf&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALTc7203525a63f93388f4ea79e89e80b036f5441bf</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4470285984/journey-final-frontier-tour-2026-shirt?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-7&amp;pro=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT566d44a436fcc4c137e06c1688363a5687770db7&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT566d44a436fcc4c137e06c1688363a5687770db7</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4466912750/journey-final-frontier-tour-2026-shirt?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-2&amp;pro=1&amp;frs=1&amp;local_signal_search=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT7cc87346594b9afa9d9e98caf12a27c5fc645431&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT7cc87346594b9afa9d9e98caf12a27c5fc645431</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4470313750/bts-arirang-world-tour-2026-svg-bundle?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-6&amp;pro=1&amp;pop=1&amp;dd=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT9b8567c41c2d1a3d18a846e795a5c920ca3ccb02&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT9b8567c41c2d1a3d18a846e795a5c920ca3ccb02</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4459895238/st-patricks-day-svg-bundle-of-50-o-lucky?ls=r&amp;ref=related-1&amp;pro=1&amp;dd=1&amp;content_source=a6e4c17a1c301715d18fff1cde510f9f%253ALTa1be640c2d7f429a10b1eae9785d8bb706c9bf48&amp;logging_key=a6e4c17a1c301715d18fff1cde510f9f%3ALTa1be640c2d7f429a10b1eae9785d8bb706c9bf48</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4470135504/heaven-on-top-2026-tour-style-album-t?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-8&amp;pro=1&amp;pop=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT52242a639fa33c5ac6a27b6e21c219656ee62796&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT52242a639fa33c5ac6a27b6e21c219656ee62796</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4469391253/boys4life-tour-shirtsweatshirt-b2k-bow?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sc_gallery-1-6&amp;pro=1&amp;sts=1&amp;plkey=EuT5L3uuuid6SYAbqvplfKbowzdc%3ALT04c9b4eb6accd9dc42ea3275eb8134497a8fd93e</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4470693269/comfort-colors-zach-bryan-shirt-with?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-41&amp;pro=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALTde2d59617824f4d6afa69e4221b15491b32722c4&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALTde2d59617824f4d6afa69e4221b15491b32722c4</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4471173718/comfort-colors-bad-omens-band-shirt-do?ls=r&amp;ref=related-4&amp;pro=1&amp;content_source=4c662e385570274d7609c7766a986ef5%253ALTedfc5a70b26edd70cb95c54fb97c82983301ab82&amp;logging_key=4c662e385570274d7609c7766a986ef5%3ALTedfc5a70b26edd70cb95c54fb97c82983301ab82</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4471168535/comfort-colors-zach-bryan-shirt-with?ls=r&amp;ref=related-3&amp;pro=1&amp;content_source=4c662e385570274d7609c7766a986ef5%253ALTa75db48c4a0f4719f9a4fb4dc509903fb6ab8276&amp;logging_key=4c662e385570274d7609c7766a986ef5%3ALTa75db48c4a0f4719f9a4fb4dc509903fb6ab8276</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4469477468/cardi-b-little-miss-drama-png-bundle?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=PNG+Cardi+B&amp;ref=sr_gallery-1-3&amp;dd=1&amp;content_source=8e9f4360-51c0-4bf8-854b-04ddce83d872%253ALTc47d248e2753ed53bc6689e72e65c5d65e61bd7d&amp;organic_search_click=1&amp;logging_key=8e9f4360-51c0-4bf8-854b-04ddce83d872%3ALTc47d248e2753ed53bc6689e72e65c5d65e61bd7d</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4466051224/cardi-b-little-miss-drama-png-bundle-20?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=PNG+Cardi+B&amp;ref=sr_gallery-1-6&amp;pro=1&amp;dd=1&amp;content_source=8e9f4360-51c0-4bf8-854b-04ddce83d872%253ALTc30c7353a907523615909f265cc4f4d3b73d25e1&amp;organic_search_click=1&amp;logging_key=8e9f4360-51c0-4bf8-854b-04ddce83d872%3ALTc30c7353a907523615909f265cc4f4d3b73d25e1</t>
+  </si>
+  <si>
+    <t>LH1703</t>
   </si>
 </sst>
 </file>
@@ -124,16 +139,16 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -151,7 +166,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -434,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -456,135 +471,170 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="120.75" thickBot="1">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="180.75" thickBot="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1"/>
@@ -877,42 +927,6 @@
     <row r="89" spans="1:2">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="1"/>
-      <c r="B90" s="2"/>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="1"/>
-      <c r="B91" s="2"/>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="1"/>
-      <c r="B92" s="2"/>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="1"/>
-      <c r="B93" s="2"/>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="1"/>
-      <c r="B94" s="2"/>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="1"/>
-      <c r="B95" s="2"/>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="1"/>
-      <c r="B96" s="2"/>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="1"/>
-      <c r="B97" s="2"/>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input/linkSanPham.xlsx
+++ b/input/linkSanPham.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Name Acc</t>
   </si>
@@ -41,59 +41,17 @@
     <t>VPN-TOOL-THIET</t>
   </si>
   <si>
-    <t>https://www.etsy.com/listing/4468133183/harry-styles-tour-2026-t-shirt-2-sided?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-1&amp;pro=1&amp;pop=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT49d7bb0973ada13d81acc0b91a5c26240b4c9070&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT49d7bb0973ada13d81acc0b91a5c26240b4c9070</t>
+    <t>test2503</t>
   </si>
   <si>
-    <t>https://www.etsy.com/listing/4467439062/cardi-b-little-miss-drama-png-bundle?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=digital+hot&amp;ref=sr_gallery-1-30&amp;pro=1&amp;pop=1&amp;dd=1&amp;content_source=2abb1d39-7b0f-4bc1-bb8d-d43650e25d91%253ALT15a94dab7eede1dc58bd3a80961a0e21ce6ad8dc&amp;organic_search_click=1&amp;logging_key=2abb1d39-7b0f-4bc1-bb8d-d43650e25d91%3ALT15a94dab7eede1dc58bd3a80961a0e21ce6ad8dc</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4465475509/b2k-bow-wow-boys4life-tour-png-file-b2k?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sc_gallery-1-1&amp;bes=1&amp;dd=1&amp;plkey=EuT5L3uuuid6SYAbqvplfKbowzdc%3ALTd3104fd06d8f578090cfd50cf43c7823b1f31846</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4465319382/conan-gray-wishbone-world-tour-2026-tour?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-3&amp;pop=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALTc7203525a63f93388f4ea79e89e80b036f5441bf&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALTc7203525a63f93388f4ea79e89e80b036f5441bf</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4470285984/journey-final-frontier-tour-2026-shirt?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-7&amp;pro=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT566d44a436fcc4c137e06c1688363a5687770db7&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT566d44a436fcc4c137e06c1688363a5687770db7</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4466912750/journey-final-frontier-tour-2026-shirt?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-2&amp;pro=1&amp;frs=1&amp;local_signal_search=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT7cc87346594b9afa9d9e98caf12a27c5fc645431&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT7cc87346594b9afa9d9e98caf12a27c5fc645431</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4470313750/bts-arirang-world-tour-2026-svg-bundle?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-6&amp;pro=1&amp;pop=1&amp;dd=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT9b8567c41c2d1a3d18a846e795a5c920ca3ccb02&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT9b8567c41c2d1a3d18a846e795a5c920ca3ccb02</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4459895238/st-patricks-day-svg-bundle-of-50-o-lucky?ls=r&amp;ref=related-1&amp;pro=1&amp;dd=1&amp;content_source=a6e4c17a1c301715d18fff1cde510f9f%253ALTa1be640c2d7f429a10b1eae9785d8bb706c9bf48&amp;logging_key=a6e4c17a1c301715d18fff1cde510f9f%3ALTa1be640c2d7f429a10b1eae9785d8bb706c9bf48</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4470135504/heaven-on-top-2026-tour-style-album-t?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-8&amp;pro=1&amp;pop=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALT52242a639fa33c5ac6a27b6e21c219656ee62796&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALT52242a639fa33c5ac6a27b6e21c219656ee62796</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4469391253/boys4life-tour-shirtsweatshirt-b2k-bow?ls=a&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sc_gallery-1-6&amp;pro=1&amp;sts=1&amp;plkey=EuT5L3uuuid6SYAbqvplfKbowzdc%3ALT04c9b4eb6accd9dc42ea3275eb8134497a8fd93e</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4470693269/comfort-colors-zach-bryan-shirt-with?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=tour+2026&amp;ref=sr_gallery-1-41&amp;pro=1&amp;content_source=54be35fa-09b8-4c93-a31a-78e678514eb7%253ALTde2d59617824f4d6afa69e4221b15491b32722c4&amp;organic_search_click=1&amp;logging_key=54be35fa-09b8-4c93-a31a-78e678514eb7%3ALTde2d59617824f4d6afa69e4221b15491b32722c4</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4471173718/comfort-colors-bad-omens-band-shirt-do?ls=r&amp;ref=related-4&amp;pro=1&amp;content_source=4c662e385570274d7609c7766a986ef5%253ALTedfc5a70b26edd70cb95c54fb97c82983301ab82&amp;logging_key=4c662e385570274d7609c7766a986ef5%3ALTedfc5a70b26edd70cb95c54fb97c82983301ab82</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4471168535/comfort-colors-zach-bryan-shirt-with?ls=r&amp;ref=related-3&amp;pro=1&amp;content_source=4c662e385570274d7609c7766a986ef5%253ALTa75db48c4a0f4719f9a4fb4dc509903fb6ab8276&amp;logging_key=4c662e385570274d7609c7766a986ef5%3ALTa75db48c4a0f4719f9a4fb4dc509903fb6ab8276</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4469477468/cardi-b-little-miss-drama-png-bundle?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=PNG+Cardi+B&amp;ref=sr_gallery-1-3&amp;dd=1&amp;content_source=8e9f4360-51c0-4bf8-854b-04ddce83d872%253ALTc47d248e2753ed53bc6689e72e65c5d65e61bd7d&amp;organic_search_click=1&amp;logging_key=8e9f4360-51c0-4bf8-854b-04ddce83d872%3ALTc47d248e2753ed53bc6689e72e65c5d65e61bd7d</t>
-  </si>
-  <si>
-    <t>https://www.etsy.com/listing/4466051224/cardi-b-little-miss-drama-png-bundle-20?ls=s&amp;ga_order=most_relevant&amp;ga_search_type=all&amp;ga_view_type=gallery&amp;ga_search_query=PNG+Cardi+B&amp;ref=sr_gallery-1-6&amp;pro=1&amp;dd=1&amp;content_source=8e9f4360-51c0-4bf8-854b-04ddce83d872%253ALTc30c7353a907523615909f265cc4f4d3b73d25e1&amp;organic_search_click=1&amp;logging_key=8e9f4360-51c0-4bf8-854b-04ddce83d872%3ALTc30c7353a907523615909f265cc4f4d3b73d25e1</t>
-  </si>
-  <si>
-    <t>LH1703</t>
+    <t>https://velvetcaviar.com/products/fairytale-forest-airpod-case?variant=42151234535470</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,13 +78,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -165,7 +137,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +426,7 @@
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1">
@@ -476,165 +448,67 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1"/>
